--- a/cell_demo/細胞曲線圖/20250904v8_counts.xlsx
+++ b/cell_demo/細胞曲線圖/20250904v8_counts.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\細胞產學 資料\CELL_VIABILITY_RECOG\cell_demo\細胞曲線圖\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E351A18-8FCA-4459-8BC9-CD05A0AC5DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC41CA6-45B1-45FE-8A2C-BD9FB4ED33E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5250" yWindow="990" windowWidth="21600" windowHeight="11295" xr2:uid="{3D2E740E-D629-4192-997D-18308F5645C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D2E740E-D629-4192-997D-18308F5645C6}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -347,13 +347,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -2835,9 +2832,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>66674</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2868,7 +2865,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2876,34 +2873,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -3189,13 +3186,13 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3203,13 +3200,13 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="1">
         <v>72</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>95</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="1">
         <v>107</v>
       </c>
     </row>
@@ -3217,13 +3214,13 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="1">
         <v>89</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>122</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="1">
         <v>111</v>
       </c>
     </row>
@@ -3231,13 +3228,13 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="1">
         <v>107</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>120</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="1">
         <v>114</v>
       </c>
     </row>
@@ -3245,13 +3242,13 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="1">
         <v>110</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>112</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="1">
         <v>112</v>
       </c>
     </row>
@@ -3259,13 +3256,13 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="1">
         <v>107</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>106</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="1">
         <v>114</v>
       </c>
     </row>
@@ -3273,13 +3270,13 @@
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="1">
         <v>98</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>112</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="1">
         <v>125</v>
       </c>
     </row>
@@ -3287,13 +3284,13 @@
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="1">
         <v>93</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>114</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="1">
         <v>119</v>
       </c>
     </row>
@@ -3301,13 +3298,13 @@
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="1">
         <v>90</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>113</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="1">
         <v>124</v>
       </c>
     </row>
@@ -3315,13 +3312,13 @@
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="1">
         <v>93</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>108</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="1">
         <v>118</v>
       </c>
     </row>
@@ -3329,13 +3326,13 @@
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="1">
         <v>92</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>101</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="1">
         <v>117</v>
       </c>
     </row>
@@ -3343,13 +3340,13 @@
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="1">
         <v>93</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>101</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="1">
         <v>100</v>
       </c>
     </row>
@@ -3357,13 +3354,13 @@
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="1">
         <v>95</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>101</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="1">
         <v>98</v>
       </c>
     </row>
@@ -3371,13 +3368,13 @@
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="1">
         <v>97</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>90</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="1">
         <v>90</v>
       </c>
     </row>
@@ -3385,13 +3382,13 @@
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="1">
         <v>96</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>92</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="1">
         <v>95</v>
       </c>
     </row>
@@ -3399,13 +3396,13 @@
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="1">
         <v>96</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>81</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="1">
         <v>96</v>
       </c>
     </row>
@@ -3413,13 +3410,13 @@
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="1">
         <v>96</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>93</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="1">
         <v>96</v>
       </c>
     </row>
@@ -3427,13 +3424,13 @@
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="1">
         <v>95</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>90</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="1">
         <v>88</v>
       </c>
     </row>
@@ -3441,13 +3438,13 @@
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="1">
         <v>93</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="1">
         <v>92</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="1">
         <v>64</v>
       </c>
     </row>
@@ -3455,13 +3452,13 @@
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="1">
         <v>95</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>83</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="1">
         <v>60</v>
       </c>
     </row>
@@ -3469,13 +3466,13 @@
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="1">
         <v>94</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="1">
         <v>81</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="1">
         <v>54</v>
       </c>
     </row>
@@ -3483,13 +3480,13 @@
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="1">
         <v>93</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="1">
         <v>78</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="1">
         <v>53</v>
       </c>
     </row>
@@ -3497,13 +3494,13 @@
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="1">
         <v>91</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="1">
         <v>79</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="1">
         <v>50</v>
       </c>
     </row>
@@ -3511,13 +3508,13 @@
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="1">
         <v>93</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="1">
         <v>80</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="1">
         <v>56</v>
       </c>
     </row>
@@ -3525,13 +3522,13 @@
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="1">
         <v>93</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1">
         <v>75</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="1">
         <v>55</v>
       </c>
     </row>
@@ -3539,13 +3536,13 @@
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="1">
         <v>94</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="1">
         <v>71</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="1">
         <v>49</v>
       </c>
     </row>
@@ -3553,13 +3550,13 @@
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="1">
         <v>93</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>67</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="1">
         <v>47</v>
       </c>
     </row>
@@ -3567,13 +3564,13 @@
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="1">
         <v>93</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="1">
         <v>64</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="1">
         <v>43</v>
       </c>
     </row>
@@ -3581,13 +3578,13 @@
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="1">
         <v>91</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="1">
         <v>61</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="1">
         <v>48</v>
       </c>
     </row>
@@ -3595,13 +3592,13 @@
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="1">
         <v>91</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="1">
         <v>59</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="1">
         <v>41</v>
       </c>
     </row>
@@ -3609,13 +3606,13 @@
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="1">
         <v>93</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="1">
         <v>58</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="1">
         <v>39</v>
       </c>
     </row>
@@ -3623,13 +3620,13 @@
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="1">
         <v>89</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="1">
         <v>73</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="1">
         <v>34</v>
       </c>
     </row>
@@ -3637,13 +3634,13 @@
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="1">
         <v>80</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="1">
         <v>56</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="1">
         <v>31</v>
       </c>
     </row>
@@ -3651,13 +3648,13 @@
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="1">
         <v>83</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="1">
         <v>62</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="1">
         <v>29</v>
       </c>
     </row>
@@ -3665,13 +3662,13 @@
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="1">
         <v>79</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="1">
         <v>55</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="1">
         <v>25</v>
       </c>
     </row>
@@ -3679,13 +3676,13 @@
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="1">
         <v>80</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>52</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="1">
         <v>25</v>
       </c>
     </row>
@@ -3693,13 +3690,13 @@
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="1">
         <v>76</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>51</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="1">
         <v>21</v>
       </c>
     </row>
@@ -3707,13 +3704,13 @@
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="1">
         <v>73</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>45</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="1">
         <v>19</v>
       </c>
     </row>
@@ -3721,13 +3718,13 @@
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="1">
         <v>74</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>51</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="1">
         <v>19</v>
       </c>
     </row>
@@ -3735,13 +3732,13 @@
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="1">
         <v>71</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="1">
         <v>49</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="1">
         <v>20</v>
       </c>
     </row>
@@ -3749,13 +3746,13 @@
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="1">
         <v>72</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="1">
         <v>50</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="1">
         <v>15</v>
       </c>
     </row>
@@ -3763,13 +3760,13 @@
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="1">
         <v>70</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>44</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="1">
         <v>12</v>
       </c>
     </row>
@@ -3777,13 +3774,13 @@
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="1">
         <v>66</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="1">
         <v>48</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="1">
         <v>14</v>
       </c>
     </row>
@@ -3791,13 +3788,13 @@
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="1">
         <v>66</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>49</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="1">
         <v>11</v>
       </c>
     </row>
@@ -3805,13 +3802,13 @@
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="1">
         <v>63</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="1">
         <v>45</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="1">
         <v>11</v>
       </c>
     </row>
@@ -3819,13 +3816,13 @@
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="1">
         <v>60</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="1">
         <v>48</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="1">
         <v>11</v>
       </c>
     </row>
@@ -3833,13 +3830,13 @@
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="1">
         <v>60</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="1">
         <v>34</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="1">
         <v>9</v>
       </c>
     </row>
@@ -3847,13 +3844,13 @@
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="1">
         <v>55</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="1">
         <v>31</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="1">
         <v>9</v>
       </c>
     </row>
@@ -3861,13 +3858,13 @@
       <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="1">
         <v>48</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>28</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="1">
         <v>11</v>
       </c>
     </row>
@@ -3875,13 +3872,13 @@
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="1">
         <v>49</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="1">
         <v>31</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="1">
         <v>4</v>
       </c>
     </row>
@@ -3889,13 +3886,13 @@
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="1">
         <v>47</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="1">
         <v>30</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="1">
         <v>8</v>
       </c>
     </row>
@@ -3903,13 +3900,13 @@
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="1">
         <v>44</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="1">
         <v>32</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="1">
         <v>9</v>
       </c>
     </row>
@@ -3917,13 +3914,13 @@
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="1">
         <v>44</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="1">
         <v>27</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="1">
         <v>8</v>
       </c>
     </row>
@@ -3931,13 +3928,13 @@
       <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="1">
         <v>38</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="1">
         <v>26</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="1">
         <v>6</v>
       </c>
     </row>
@@ -3945,13 +3942,13 @@
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="1">
         <v>36</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="1">
         <v>22</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="1">
         <v>6</v>
       </c>
     </row>
@@ -3959,13 +3956,13 @@
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="1">
         <v>36</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>21</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="1">
         <v>5</v>
       </c>
     </row>
@@ -3973,13 +3970,13 @@
       <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="1">
         <v>30</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="1">
         <v>21</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="1">
         <v>6</v>
       </c>
     </row>
@@ -3987,13 +3984,13 @@
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="1">
         <v>29</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="1">
         <v>16</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="1">
         <v>5</v>
       </c>
     </row>
@@ -4001,13 +3998,13 @@
       <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="1">
         <v>26</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="1">
         <v>21</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="1">
         <v>4</v>
       </c>
     </row>
@@ -4015,13 +4012,13 @@
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="1">
         <v>23</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="1">
         <v>23</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="1">
         <v>4</v>
       </c>
     </row>
@@ -4029,13 +4026,13 @@
       <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="1">
         <v>23</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="1">
         <v>13</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="1">
         <v>4</v>
       </c>
     </row>
@@ -4043,13 +4040,13 @@
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="1">
         <v>22</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>10</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="1">
         <v>5</v>
       </c>
     </row>
@@ -4057,13 +4054,13 @@
       <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="1">
         <v>19</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="1">
         <v>10</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4071,13 +4068,13 @@
       <c r="A64" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="1">
         <v>17</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>13</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64" s="1">
         <v>4</v>
       </c>
     </row>
@@ -4085,13 +4082,13 @@
       <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="1">
         <v>16</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="1">
         <v>10</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G65" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4099,13 +4096,13 @@
       <c r="A66" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="1">
         <v>11</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="1">
         <v>13</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G66" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4113,13 +4110,13 @@
       <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="1">
         <v>12</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>9</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G67" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4127,13 +4124,13 @@
       <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="1">
         <v>9</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>8</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4141,13 +4138,13 @@
       <c r="A69" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="1">
         <v>12</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="1">
         <v>10</v>
       </c>
-      <c r="G69" s="3">
+      <c r="G69" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4155,13 +4152,13 @@
       <c r="A70" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="1">
         <v>10</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="1">
         <v>10</v>
       </c>
-      <c r="G70" s="3">
+      <c r="G70" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4169,13 +4166,13 @@
       <c r="A71" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="1">
         <v>9</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>6</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G71" s="1">
         <v>4</v>
       </c>
     </row>
@@ -4183,13 +4180,13 @@
       <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="1">
         <v>9</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="1">
         <v>5</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4197,13 +4194,13 @@
       <c r="A73" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="1">
         <v>8</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>3</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G73" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4211,13 +4208,13 @@
       <c r="A74" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="1">
         <v>11</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="1">
         <v>7</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G74" s="1">
         <v>4</v>
       </c>
     </row>
@@ -4225,13 +4222,13 @@
       <c r="A75" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="1">
         <v>8</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75" s="1">
         <v>8</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75" s="1">
         <v>4</v>
       </c>
     </row>
@@ -4239,13 +4236,13 @@
       <c r="A76" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="1">
         <v>6</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="1">
         <v>5</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G76" s="1">
         <v>4</v>
       </c>
     </row>
@@ -4253,13 +4250,13 @@
       <c r="A77" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="1">
         <v>7</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="1">
         <v>4</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G77" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4267,13 +4264,13 @@
       <c r="A78" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="1">
         <v>7</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>8</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G78" s="1">
         <v>4</v>
       </c>
     </row>
@@ -4281,13 +4278,13 @@
       <c r="A79" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="1">
         <v>6</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="1">
         <v>5</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G79" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4295,13 +4292,13 @@
       <c r="A80" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80" s="1">
         <v>6</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="1">
         <v>4</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G80" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4309,13 +4306,13 @@
       <c r="A81" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81" s="1">
         <v>3</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="1">
         <v>2</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G81" s="1">
         <v>3</v>
       </c>
     </row>
@@ -4323,13 +4320,13 @@
       <c r="A82" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82" s="1">
         <v>5</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="1">
         <v>3</v>
       </c>
-      <c r="G82" s="3">
+      <c r="G82" s="1">
         <v>3</v>
       </c>
     </row>
